--- a/daily_matches/job_matches_2026-06-25.xlsx
+++ b/daily_matches/job_matches_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer on-site)</t>
+          <t>Senior Architect, Technology I</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Mettawa, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, MLflow, CI/CD, Terraform, Snowflake, Databricks, PySpark</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, S3, Glue, Athena, Redshift, CI/CD, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c91ab31afe36f91</t>
+          <t>https://www.indeed.com/viewjob?jk=6bde36b833417f68</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer on-site)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ziosk</t>
+          <t>Mad Mobile</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Synapse, Data Lake, MLflow, CI/CD, Terraform, Snowflake, Databricks, PySpark</t>
+          <t>RAG, Copilot, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, Git, Kafka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,102 +531,102 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13b180e2e10be4d8</t>
+          <t>https://www.indeed.com/viewjob?jk=912fd59f7f797fb3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Gallagher</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Rolling Meadows, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80744870ee084082</t>
+          <t>https://www.indeed.com/viewjob?jk=d96154d6390ad71f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Scientist III, Software Engineer, Upstream Process Development</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Thermo Fisher Scientific</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Grand Island, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=578dcb2cdfe7e8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=ff0934ab4205ec3f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Full Stack Software Engineer</t>
+          <t>System Infrastructure / Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Bay Systems Consulting, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Docker, CI/CD, Terraform, Git, Kafka, PostgreSQL, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,194 +636,194 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78859929316f4cba</t>
+          <t>https://www.indeed.com/viewjob?jk=f041e701ae1817f7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Applied AI Engineer (LLMs, Agents, and Healthcare AI)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Human Longevity</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>South San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Copilot, Prompt Engineering, Git, Python, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1c17468b23ff011</t>
+          <t>https://www.indeed.com/viewjob?jk=2217e4237a92f162</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17342d412700ed77</t>
+          <t>https://www.indeed.com/viewjob?jk=baca40ff3de350b4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PhD Student in AI research</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, SQL, R</t>
+          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8673766c23a39840</t>
+          <t>https://www.indeed.com/viewjob?jk=13f6a761f80f3a29</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Middle–Senior Software / Data Engineer, AI Enablement &amp; Data Platform Migration</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DataArt</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Annapolis, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Apache Airflow, Snowflake, Databricks, NoSQL, Python, SQL, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3094b458dcbd5120</t>
+          <t>https://www.indeed.com/viewjob?jk=b9a5428cd66cf33e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Platform Consultant - Technology Risk &amp; Compliance</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Allstate Insurance</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7889e892adfae1a4</t>
+          <t>https://www.indeed.com/viewjob?jk=be1d010a902f7d0c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Demo Platform Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Kobie Marketing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,46 +832,46 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=269d03aac02123d7</t>
+          <t>https://www.indeed.com/viewjob?jk=2165a914d526eec0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer -Alerts</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>National Hockey League</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Git, Kafka, SQL, R, Java, Optimization</t>
+          <t>AI Engineer, Generative AI, RAG, Cortex, CI/CD, Git, Snowflake, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f04e57f996d3baa2</t>
+          <t>https://www.indeed.com/viewjob?jk=28e952483966b5ec</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Voice Backend Software Engineer (Node.js and Java) | Remote | US</t>
+          <t>Machine Learning Engineer - Generative AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sutherland</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, PostgreSQL, SQL, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c13df235f5ffd6c0</t>
+          <t>https://www.indeed.com/viewjob?jk=5f07583592d02703</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Vision Systems Engineer, Automation Engineering</t>
+          <t>Sr. Production Support Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, CI/CD, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f0d638e3f33225b</t>
+          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II - Test Automation Engineer</t>
+          <t>Postdoctoral Researcher</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18647fd5d1c3c5b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a51de5e934f58b5c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>PhD Student in AI research</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Kafka, MongoDB, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b27f19d1b158344</t>
+          <t>https://www.indeed.com/viewjob?jk=418ac630eeb0d108</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Architect, Professional Services</t>
+          <t>Network Software Test Engineer I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alteryx</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Roseville, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Snowflake, Databricks, Tableau, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d766c608c497a3f7</t>
+          <t>https://www.indeed.com/viewjob?jk=a2022f82acde1608</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Prinicpal Software Engineer - Data Engineering &amp; Streaming Primitives</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, SQL, R, Java</t>
+          <t>Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da7d1704b499dd2b</t>
+          <t>https://www.indeed.com/viewjob?jk=dfe5425cbba48f6d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Solutions Architect - Omnichannel</t>
+          <t>Agentic AI Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Five Below</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, Git, Snowflake, Databricks, Kafka, R, Scala</t>
+          <t>AI Engineer, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f058ca30d1bcc8cd</t>
+          <t>https://www.indeed.com/viewjob?jk=b7ccbf26f96969e0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CRM Developer</t>
+          <t>Research Computational and Data Scientist II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>CHOC Children's</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cockeysville, MD, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Power BI, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Git, Python, SQL, R, Bayesian</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d65ef3ca199367ae</t>
+          <t>https://www.indeed.com/viewjob?jk=63fe88a9289fd9c2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Jr Data Scientist</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Focus Camera</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Generative AI, Docker, Kubernetes, CI/CD, Git, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, Git, MySQL, Power BI, Python, SQL, R, Scala, Optimization, Bayesian</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=737855e73614afc1</t>
+          <t>https://www.indeed.com/viewjob?jk=e0c29d2f00fc6548</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. React JS Developer w/d Python Expert</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>I8IS INC.</t>
+          <t>Indica Labs</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Git, Python, R, Java, Scala, Optimization</t>
+          <t>S3, EC2, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54078be2f9a02b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=d084fd00ffbebf27</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Norfolk, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,17 +1256,227 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Terraform, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80fa9c281fc7d183</t>
+          <t>https://www.indeed.com/viewjob?jk=039905fed968e729</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Norfolk, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Terraform, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef1c86366284410a</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineering PMTS</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Salesforce</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6390aaf16b28ee5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer - Cloud Automation &amp; AI Systems</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46159a46f0944948</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Caterpillar</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=61bee7004ecedde8</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Software Engineer I</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Aledade, Inc.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=271809339c364fd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Backend Engineer AI (Agent Systems).</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>VASERJOB</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8df2574bb773a06f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-25.xlsx
+++ b/daily_matches/job_matches_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Architect, Technology I</t>
+          <t>LoopNet - Senior Software Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mettawa, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.1</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, LLaMA, S3, Glue, Athena, Redshift, CI/CD, Git</t>
+          <t>RAG, Copilot, S3, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bde36b833417f68</t>
+          <t>https://www.indeed.com/viewjob?jk=1582817466d60077</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>AI Engineer (Data Scientist)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mad Mobile</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes, Git, Kafka</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, PyTorch, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912fd59f7f797fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=55e24e44fc107cc9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gallagher</t>
+          <t>Zions Bancorporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rolling Meadows, IL, US USA</t>
+          <t>Midvale, UT, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Prompt Engineering, Kubernetes, CI/CD</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d96154d6390ad71f</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd7548d0dd278d5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Scientist III, Software Engineer, Upstream Process Development</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Grand Island, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, ChromaDB, Prompt Engineering, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff0934ab4205ec3f</t>
+          <t>https://www.indeed.com/viewjob?jk=35215fc5c1ce82a6</t>
         </is>
       </c>
     </row>
@@ -613,7 +613,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bay Systems Consulting, Inc.</t>
+          <t>LTD Global</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,7 +622,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -636,242 +636,242 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f041e701ae1817f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d06030c01a8fa691</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer III - Big Data &amp; AWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
+          <t>RAG, S3, Glue, Redshift, Terraform, Databricks, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2217e4237a92f162</t>
+          <t>https://www.indeed.com/viewjob?jk=e8a9e089237396a3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>AI/ML Engineer - Mid-Career - Level 3</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
+          <t>AI Engineer, LangChain, RAG, Gemini, TensorFlow, PyTorch, OpenCV, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=baca40ff3de350b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f82902dcd8040459</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>DIVERGENT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f6a761f80f3a29</t>
+          <t>https://www.indeed.com/viewjob?jk=047f6164eb12d8d8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data and Analytics - AI Engineer I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>WoodmenLife</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9a5428cd66cf33e</t>
+          <t>https://www.indeed.com/viewjob?jk=337d14d24d714dec</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data and Analytics - AI Engineer I</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>WoodmenLife</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
+          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Snowflake, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be1d010a902f7d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=97deaba49abbe9d9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kobie Marketing</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Cortex, MLflow, Docker, AKS, Git, Snowflake, Python</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2165a914d526eec0</t>
+          <t>https://www.indeed.com/viewjob?jk=bf6dc9ebd6a9ade1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Product Engineer - AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>National Hockey League</t>
+          <t>ALMA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Cortex, CI/CD, Git, Snowflake, Databricks, Python, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, FastAPI, PostgreSQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e952483966b5ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ec2f72ff929aaf9a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer - Generative AI</t>
+          <t>Senior Software Engineer, Back-End (Payments)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Collectors</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python</t>
+          <t>RAG, Kubernetes, Git, Kafka, PostgreSQL, NoSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f07583592d02703</t>
+          <t>https://www.indeed.com/viewjob?jk=ebeb2570baaf1984</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Production Support Engineer</t>
+          <t>Sr.Dot Net Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Git, MongoDB, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05e52cde67bec12e</t>
+          <t>https://www.indeed.com/viewjob?jk=2cde7eded2299539</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Postdoctoral Researcher</t>
+          <t>Sr.Dot Net Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,497 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a51de5e934f58b5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>PhD Student in AI research</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>University of Utah</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, SQL, R</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=418ac630eeb0d108</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Network Software Test Engineer I</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Roseville, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2022f82acde1608</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Prinicpal Software Engineer - Data Engineering &amp; Streaming Primitives</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Snowflake</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, Kafka, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfe5425cbba48f6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Agentic AI Architect</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, FAISS, Pinecone, Prompt Engineering, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b7ccbf26f96969e0</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Research Computational and Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CHOC Children's</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Orange, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, Keras, Git, Python, SQL, R, Bayesian</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=63fe88a9289fd9c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Jr Data Scientist</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Focus Camera</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Data Scientist, Git, MySQL, Power BI, Python, SQL, R, Scala, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0c29d2f00fc6548</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Indica Labs</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Albuquerque, NM, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>S3, EC2, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d084fd00ffbebf27</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Norfolk, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Terraform, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=039905fed968e729</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Norfolk, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Terraform, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef1c86366284410a</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Software Engineering PMTS</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Salesforce</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6390aaf16b28ee5a</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer - Cloud Automation &amp; AI Systems</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Terraform, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=46159a46f0944948</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Caterpillar</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>10</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61bee7004ecedde8</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Aledade, Inc.</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=271809339c364fd6</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Backend Engineer AI (Agent Systems).</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>VASERJOB</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, PyTorch, Docker, Kubernetes, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8df2574bb773a06f</t>
+          <t>https://www.indeed.com/viewjob?jk=1cc292d97aa3a39e</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-25.xlsx
+++ b/daily_matches/job_matches_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>LoopNet - Senior Software Engineer</t>
+          <t>Software Engineer III - AWS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>13.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, BigQuery, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks</t>
+          <t>RAG, Glue, Athena, Redshift, Data Lake, CI/CD, Terraform, Redshift, Python, R</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,497 +496,42 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1582817466d60077</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed33c1af1fbb6ee</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer (Data Scientist)</t>
+          <t>Applied AI Software Engineer, Factory Software</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, Prompt Engineering, PyTorch, FastAPI, Docker, Kubernetes</t>
+          <t>RAG, Prompt Engineering, CI/CD, Kafka, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55e24e44fc107cc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Zions Bancorporation</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Midvale, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, MongoDB, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8bd7548d0dd278d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>AI Developer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Glint Tech Solutions</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Pinecone, ChromaDB, Prompt Engineering, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=35215fc5c1ce82a6</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>System Infrastructure / Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>LTD Global</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Berkeley, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d06030c01a8fa691</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Software Engineer III - Big Data &amp; AWS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>RAG, S3, Glue, Redshift, Terraform, Databricks, Redshift, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e8a9e089237396a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer - Mid-Career - Level 3</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Lockheed Martin</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Fort Worth, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, TensorFlow, PyTorch, OpenCV, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f82902dcd8040459</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>DIVERGENT</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Torrance, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=047f6164eb12d8d8</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Data and Analytics - AI Engineer I</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>WoodmenLife</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=337d14d24d714dec</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Data and Analytics - AI Engineer I</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>WoodmenLife</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, TensorFlow, PyTorch, Git, Snowflake, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=97deaba49abbe9d9</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R, Scala</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf6dc9ebd6a9ade1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Product Engineer - AI</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ALMA</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, FastAPI, PostgreSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec2f72ff929aaf9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Back-End (Payments)</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Collectors</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Git, Kafka, PostgreSQL, NoSQL, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebeb2570baaf1984</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Sr.Dot Net Developer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2cde7eded2299539</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Sr.Dot Net Developer</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1cc292d97aa3a39e</t>
+          <t>https://www.indeed.com/viewjob?jk=61ed235ba1244083</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-25.xlsx
+++ b/daily_matches/job_matches_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - AWS</t>
+          <t>Artificial Intelligence/Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Glue, Athena, Redshift, Data Lake, CI/CD, Terraform, Redshift, Python, R</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, PyTorch, Glue, Redshift, Synapse, MLflow, Docker, AKS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,42 +496,742 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ed33c1af1fbb6ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a074a785ce24052f</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Applied AI Software Engineer, Factory Software</t>
+          <t>Senior Application Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Redshift, FastAPI, Docker, CI/CD, Git, Snowflake, Databricks, Redshift</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b1d7e70102157f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Globant</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Data Scientist, TensorFlow, PyTorch, Azure ML, MLflow, Docker, CI/CD, Databricks, Hadoop, NoSQL</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0725cc4f521729f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (PHP)</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NMI</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4716c280fcc00d98</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Software Engineer - Application Consultant</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, S3, FastAPI, CI/CD, GitHub Actions, Terraform, Git, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=649b76151ccd01db</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Software Engineer - Application Consultant</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kyndryl</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Research Triangle Park, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, S3, FastAPI, CI/CD, GitHub Actions, Terraform, Git, MySQL, Python</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e983e1a21daa953c</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=058c5e4a7da45a32</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Axon</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Git, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c66d1722dc1904af</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Python Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Globant</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>FastAPI, Docker, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6d21f70ad7aca36</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Disney Experiences</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Orlando, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Copilot, Git, MongoDB, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ee842c7c5643d0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>[Remote] Senior FullStack Platform Software Engineer- Clinical Digital Assistant</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1a152297c2ff6df</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Associate - Data Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>New York Life</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Glue, Git, Databricks, PySpark, Kafka, SQL, R</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cab0fb5e8b841018</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Scientist IV - (1-2 Year Duration/Funding)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kaiser Permanente</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, AKS, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65dcc38c63ea4d42</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Data Scientist IV - (1-2 Year Duration/Funding)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kaiser Permanente</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pleasanton, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, AKS, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=291499a92fc58e61</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Security Engineer</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Medal</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d497ea2609f3fc01</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Atria Health and Research Institute</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Hugging Face, PyTorch, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b3ca3ee7a4c707b</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cargill</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Wayzata, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, XGBoost, LightGBM, Tableau, Power BI, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=861569919fb17a44</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>AI-Focused Software Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>osp labs hiring for us based mnc</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
         <v>10</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, CI/CD, Kafka, MySQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=61ed235ba1244083</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1040dde3fd7cfeb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebe42509d30b66ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33804da82ef423eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SOSi</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>El Paso, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10360f376829fb7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Medal</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, GitHub Actions, Terraform, Git, SQL, R, Java, Optimization, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=288b9bb23441b40f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-25.xlsx
+++ b/daily_matches/job_matches_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence/Machine Learning Engineer</t>
+          <t>Databricks Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Palmetto Tech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, PyTorch, Glue, Redshift, Synapse, MLflow, Docker, AKS</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Kinesis, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a074a785ce24052f</t>
+          <t>https://www.indeed.com/viewjob?jk=d57ef47d055269a5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Application Engineer</t>
+          <t>Sr Software Engineer I</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, FastAPI, Docker, CI/CD, Git, Snowflake, Databricks, Redshift</t>
+          <t>Data Scientist, Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, Cassandra</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1d7e70102157f1</t>
+          <t>https://www.indeed.com/viewjob?jk=b11810a6c43504b5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>GCP Spanner Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Azure ML, MLflow, Docker, CI/CD, Databricks, Hadoop, NoSQL</t>
+          <t>RAG, BigQuery, Data Lake, Dataflow, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0725cc4f521729f5</t>
+          <t>https://www.indeed.com/viewjob?jk=76401a227b65d3e8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PHP)</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NMI</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, Git, MySQL, Python, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Data Lake, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4716c280fcc00d98</t>
+          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer - Application Consultant</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, FastAPI, CI/CD, GitHub Actions, Terraform, Git, MySQL, Python</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Data Lake, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=649b76151ccd01db</t>
+          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer - Application Consultant</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kyndryl</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, S3, FastAPI, CI/CD, GitHub Actions, Terraform, Git, MySQL, Python</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Data Lake, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e983e1a21daa953c</t>
+          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Software Engineer, Data Science</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ExtraHop Networks</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java</t>
+          <t>RAG, S3, EC2, FastAPI, Docker, Kubernetes, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=058c5e4a7da45a32</t>
+          <t>https://www.indeed.com/viewjob?jk=a0e77b1dd58e37d2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Full Stack AI Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Axon</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, Terraform, Git, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, SQL</t>
+          <t>LangChain, RAG, BigQuery, FastAPI, Git, BigQuery, PostgreSQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c66d1722dc1904af</t>
+          <t>https://www.indeed.com/viewjob?jk=e01424994cfb3518</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Python Engineer</t>
+          <t>IS Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Menards</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, CI/CD, Terraform, Git, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d21f70ad7aca36</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8cc0d2a437f129</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - 2373458</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Git, MongoDB, NoSQL, Python, SQL, R, Java</t>
+          <t>CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Tableau, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,94 +811,94 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ee842c7c5643d0b</t>
+          <t>https://www.indeed.com/viewjob?jk=ff932a257a601c95</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[Remote] Senior FullStack Platform Software Engineer- Clinical Digital Assistant</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Flexday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, Git, Kafka, Python, R, Java, Scala</t>
+          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Docker, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1a152297c2ff6df</t>
+          <t>https://www.indeed.com/viewjob?jk=053298a142fbcf59</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate - Data Engineer</t>
+          <t>AI Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Escalent</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Glue, Git, Databricks, PySpark, Kafka, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cab0fb5e8b841018</t>
+          <t>https://www.indeed.com/viewjob?jk=72ced5e68aed0c4e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist IV - (1-2 Year Duration/Funding)</t>
+          <t>L2 Support Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>Blitzy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, AKS, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65dcc38c63ea4d42</t>
+          <t>https://www.indeed.com/viewjob?jk=ce57299fdaf06201</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Scientist IV - (1-2 Year Duration/Funding)</t>
+          <t>Artificial Intelligence Intern</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Kaiser Permanente</t>
+          <t>Next G Corp</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pleasanton, CA, US USA</t>
+          <t>Carolina, PR, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Docker, Kubernetes, AKS, Power BI, Python, SQL, R, Scala</t>
+          <t>Generative AI, Gemini, Copilot, Prompt Engineering, Git, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291499a92fc58e61</t>
+          <t>https://www.indeed.com/viewjob?jk=38b79e4977364d1e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Security Engineer</t>
+          <t>Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>Elite Insurance Partners</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, SQL, R</t>
+          <t>FastAPI, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d497ea2609f3fc01</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a8880c4d1d7e08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>IS Quality Assurance Senior Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Atria Health and Research Institute</t>
+          <t>Menards</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eau Claire, WI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Hugging Face, PyTorch, Git, Snowflake, Tableau, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b3ca3ee7a4c707b</t>
+          <t>https://www.indeed.com/viewjob?jk=fb8ca0eeca0894a2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Analyst (Data Solutions)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cargill</t>
+          <t>The Coca-Cola Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Wayzata, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, XGBoost, LightGBM, Tableau, Power BI, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Data Lake, Git, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861569919fb17a44</t>
+          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI-Focused Software Engineer</t>
+          <t>Software Development Engineer, AI Platform</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>osp labs hiring for us based mnc</t>
+          <t>Adobe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Prompt Engineering, CI/CD, Git, Python, R, Scala</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1040dde3fd7cfeb8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c3e02471a13e988</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineering - AI &amp; Enterprise Systems</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AT&amp;T</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Kafka, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebe42509d30b66ed</t>
+          <t>https://www.indeed.com/viewjob?jk=94bf1ad9bc23905e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Copilot, Cortex, Kubernetes, Terraform, Git, Snowflake, Databricks, Kafka, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33804da82ef423eb</t>
+          <t>https://www.indeed.com/viewjob?jk=c06e0a1c1064a596</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SOSi</t>
+          <t>Moody's</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>El Paso, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R</t>
+          <t>S3, Git, Hadoop, PostgreSQL, MongoDB, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,42 +1196,357 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10360f376829fb7a</t>
+          <t>https://www.indeed.com/viewjob?jk=76da2dc311d12db7</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Fullstack Engineer</t>
+          <t>Ontology Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Medal</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Git, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=178a5e6f1886f45d</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer, AI-Assisted Product Engineering</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Avalara</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53c303a077be6b29</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Sr. Software Development Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Avalara</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f66564a2b76f5511</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>AI Software Developer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FlyExclusive</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Copilot, PyTorch, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1f45ecc42e651f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Software Engineer I, Machine Learning</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Hugging Face, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27b25df911a5f811</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Data Security Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="D28" t="n">
         <v>10</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, GitHub Actions, Terraform, Git, SQL, R, Java, Optimization, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=288b9bb23441b40f</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd127384006a98d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Account Executive</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Rocket Software</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3447968f04a5492</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Avalara</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, CI/CD, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=877aa4d2da15f605</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sonny's Enterprises, Inc</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Milton Cat</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Milford, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=51896eda1ee9d955</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-06-25.xlsx
+++ b/daily_matches/job_matches_2026-06-25.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Remote</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Palmetto Tech</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>24.4</v>
+        <v>21.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Hugging Face, Prompt Engineering, Kinesis, MLflow, CI/CD</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Copilot, Pinecone, Prompt Engineering, S3, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57ef47d055269a5</t>
+          <t>https://www.indeed.com/viewjob?jk=a2fdb23c6c263875</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Software Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>IvoryCloud</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, Cassandra</t>
+          <t>RAG, Redshift, Synapse, Kinesis, CI/CD, Git, Snowflake, Databricks, Redshift, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b11810a6c43504b5</t>
+          <t>https://www.indeed.com/viewjob?jk=c61bc90da42df2de</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>GCP Spanner Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, Dataflow, CI/CD, GitHub Actions, Terraform, Git, BigQuery, Kafka</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, AWS SageMaker, MLflow, CI/CD, Databricks</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76401a227b65d3e8</t>
+          <t>https://www.indeed.com/viewjob?jk=258953b893df6138</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Data Lake, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, XGBoost, Snowflake, Databricks, Power BI, Matplotlib, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29685a938223251</t>
+          <t>https://www.indeed.com/viewjob?jk=85b48e9dbca3025c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Sr. Associate Software Engineer (Healthcare Data Integration)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Data Lake, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Git, Kafka, PostgreSQL, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92a7ce3bbe941f36</t>
+          <t>https://www.indeed.com/viewjob?jk=c5cc7c095dc341df</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Data Lake, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2f78c4c8ef75c2</t>
+          <t>https://www.indeed.com/viewjob?jk=f0994645aa6017c3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Data Science</t>
+          <t>Senior Data Engineer, AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ExtraHop Networks</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, FastAPI, Docker, Kubernetes, Terraform, Git, PostgreSQL, Python</t>
+          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0e77b1dd58e37d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e0ab478702c96db5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Full Stack AI Developer</t>
+          <t>UX Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>GRVTY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LangChain, RAG, BigQuery, FastAPI, Git, BigQuery, PostgreSQL, NoSQL, Python, SQL</t>
+          <t>S3, EC2, Docker, Kubernetes, Git, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e01424994cfb3518</t>
+          <t>https://www.indeed.com/viewjob?jk=46661d14e600461a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>IS Quality Assurance Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Menards</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R</t>
+          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, BigQuery, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8cc0d2a437f129</t>
+          <t>https://www.indeed.com/viewjob?jk=ebd87ad332ddc84b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2373458</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Tableau, Power BI, SQL, R</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff932a257a601c95</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd1487e7d0fd7</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>AI Strategic Partnerships Solution Architect</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Flexday</t>
+          <t>Palo Alto Networks</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, Docker, CI/CD, Python, SQL</t>
+          <t>LangChain, RAG, LLaMA, Mistral, Prompt Engineering, GCP Vertex AI, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=053298a142fbcf59</t>
+          <t>https://www.indeed.com/viewjob?jk=6c3b4d81fad6c850</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Infrastructure Engineer</t>
+          <t>Sr. Software Engineer - Provider Access (Remote)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Escalent</t>
+          <t>Rula</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ced5e68aed0c4e</t>
+          <t>https://www.indeed.com/viewjob?jk=287ca05acdd17a9f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L2 Support Engineer</t>
+          <t>Data Engineer, Finance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Blitzy</t>
+          <t>Motion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Git, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce57299fdaf06201</t>
+          <t>https://www.indeed.com/viewjob?jk=a49c234a0c6d1d83</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Intern</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Next G Corp</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Carolina, PR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, Gemini, Copilot, Prompt Engineering, Git, Tableau, Power BI, Python, SQL, R</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, spaCy, NLTK, Docker, Git, Polars, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b79e4977364d1e</t>
+          <t>https://www.indeed.com/viewjob?jk=22063ed6543857e3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>Data Scientist II - Scientific AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Elite Insurance Partners</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FastAPI, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, SQL, R, Java</t>
+          <t>Data Scientist, LangChain, RAG, PyTorch, Keras, Git, Matplotlib, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a8880c4d1d7e08</t>
+          <t>https://www.indeed.com/viewjob?jk=8e8dcd338b09d764</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>IS Quality Assurance Senior Engineer</t>
+          <t>PaaS-SaaS-DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Menards</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eau Claire, WI, US USA</t>
+          <t>Warren, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java, Scala</t>
+          <t>RAG, FastAPI, AKS, Terraform, Git, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb8ca0eeca0894a2</t>
+          <t>https://www.indeed.com/viewjob?jk=3ded9f2625d01882</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Analyst (Data Solutions)</t>
+          <t>Technology Risk Specialist | Technology Risk Management</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Coca-Cola Company</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, Gemini, Prompt Engineering, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,19 +1056,19 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa2ec42f2e29989e</t>
+          <t>https://www.indeed.com/viewjob?jk=f52c3cd0ed0da8e9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Development Engineer, AI Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Adobe</t>
+          <t>AiPrise</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, LangChain, RAG, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, Terraform, NoSQL, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c3e02471a13e988</t>
+          <t>https://www.indeed.com/viewjob?jk=321ab7e09526522f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineering - AI &amp; Enterprise Systems</t>
+          <t>SEO Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AT&amp;T</t>
+          <t>iPullRank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Docker, Kubernetes, CI/CD, Kafka, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, BigQuery, Git, BigQuery, MySQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94bf1ad9bc23905e</t>
+          <t>https://www.indeed.com/viewjob?jk=53ab38ad5bd475b1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>SEO Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>iPullRank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Copilot, Cortex, Kubernetes, Terraform, Git, Snowflake, Databricks, Kafka, R, Scala</t>
+          <t>Generative AI, RAG, BigQuery, Git, BigQuery, MySQL, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c06e0a1c1064a596</t>
+          <t>https://www.indeed.com/viewjob?jk=dad45928a5960af4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Software Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Moody's</t>
+          <t>FlyExclusive</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>S3, Git, Hadoop, PostgreSQL, MongoDB, Python, SQL, R, Java, Scala</t>
+          <t>Copilot, PyTorch, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76da2dc311d12db7</t>
+          <t>https://www.indeed.com/viewjob?jk=d94125a69153e2fe</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Ontology Engineer</t>
+          <t>Software Engineer III - Developer Platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,174 +1221,174 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, GitHub Actions, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178a5e6f1886f45d</t>
+          <t>https://www.indeed.com/viewjob?jk=8766a121df024702</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer, AI-Assisted Product Engineering</t>
+          <t>Senior IT Cloud Engineer – AI Driven Operations &amp; Platform Engineering</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Avalara</t>
+          <t>Prologis</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, NoSQL, SQL, R, Scala</t>
+          <t>LangChain, RAG, S3, EC2, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53c303a077be6b29</t>
+          <t>https://www.indeed.com/viewjob?jk=0b60417222696005</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Software Engineer, Full Stack, Level 4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Avalara</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f66564a2b76f5511</t>
+          <t>https://www.indeed.com/viewjob?jk=b420e87ab4dc187f</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI Software Developer</t>
+          <t>Software Engineer, Full Stack, Level 5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>FlyExclusive</t>
+          <t>Snap Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Copilot, PyTorch, CI/CD, Git, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, Kubernetes, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f45ecc42e651f8</t>
+          <t>https://www.indeed.com/viewjob?jk=ff3b7e044d635001</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer I, Machine Learning</t>
+          <t>US Tech - AI Engineering Senior Associate</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PwC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hugging Face, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Git, Python, R, Java</t>
+          <t>AI Engineer, Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b25df911a5f811</t>
+          <t>https://www.indeed.com/viewjob?jk=00c6f96c5afca81e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Security Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Quest Global</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BigQuery, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, BigQuery, SQL, R</t>
+          <t>RAG, S3, EC2, Kinesis, Docker, CI/CD, Terraform, Git, R</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd127384006a98d5</t>
+          <t>https://www.indeed.com/viewjob?jk=ab67feb1ad7a9c00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Account Executive</t>
+          <t>Ontology Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Rocket Software</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Snowflake, Databricks, BigQuery, Redshift, R, Scala</t>
+          <t>RAG, Snowflake, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3447968f04a5492</t>
+          <t>https://www.indeed.com/viewjob?jk=e742d7a7e322e34a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Avalara</t>
+          <t>US Mobile</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Hugging Face, Prompt Engineering, CI/CD, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Redshift, Redshift, Tableau, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=877aa4d2da15f605</t>
+          <t>https://www.indeed.com/viewjob?jk=47eebdde2d5c5ebc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Manufacturing Solutions Specialist, Marietta Job</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Sonny's Enterprises, Inc</t>
+          <t>Armstrong World Industries</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marietta, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Git, Power BI, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f7c892f9988b1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f538deb46c7ee3d6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Business Intelligence Engineer - Long Beach, CA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Milton Cat</t>
+          <t>Hydrafacial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Milford, MA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,192 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Python, SQL, R, Scala</t>
+          <t>CI/CD, Git, Snowflake, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e11fa47875d4b9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Infrastructure Storage</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Lambda</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51896eda1ee9d955</t>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=92c48de180abef92</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Infrastructure Storage</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lambda</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a4b8fa1a26276be5</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Infrastructure Storage</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Lambda</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=99245fc03101912b</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sr Data Scientist - Statistics</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>United Airlines</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Python, SQL, R, Java, Optimization, Bayesian, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b9e514ea9eb69e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Sr. Specialist, Yield Management - GTM AA Data Scientist</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Python, SQL, R, Scala, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c498efcfdc19b465</t>
         </is>
       </c>
     </row>
